--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3232,7 +3232,7 @@
         <v>126808631</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126808661</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3232,7 +3232,7 @@
         <v>126808631</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126808661</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3232,7 +3232,7 @@
         <v>126808631</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126808661</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3232,7 +3232,7 @@
         <v>126808631</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126808661</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3465,6 +3465,107 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127885511</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>967</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Påranävamyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>498268</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6824631</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>127885511</v>
       </c>
       <c r="B30" t="n">
-        <v>79115</v>
+        <v>79118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>127885511</v>
       </c>
       <c r="B30" t="n">
-        <v>79118</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>127885511</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79127</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>127885511</v>
       </c>
       <c r="B30" t="n">
-        <v>79127</v>
+        <v>79178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>127885511</v>
       </c>
       <c r="B30" t="n">
-        <v>79178</v>
+        <v>79182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34821-2025 artfynd.xlsx
+++ b/artfynd/A 34821-2025 artfynd.xlsx
@@ -3232,7 +3232,7 @@
         <v>126808631</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126808661</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
